--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_SC.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_SC.xlsx
@@ -2,27 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="Re0666c0035ea496e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Rb1c7ddf446564e3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="Rfb8f1f82e9904c2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R6024315380a44444"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R56a8e31c9c2a45a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R776f2af64b894f0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R44a9fd3ceaf3408b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R97aa0d59e49540cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R5caf7b3ff32a4c77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Rea12232cacaa4877"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R141fef85200a4c49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R75c719b93e8d43f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R1c4710ec62b34ad7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Re8c4c3eaff554566"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R6085b33b36b74a16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="Re2da978fec784dc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R8c7b23577f4844a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R9a44d153c6674f93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R8cd40cc87ab3417b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R43dd95bb09db446a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="Rd02f11b91a394078"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R085b7f42a1644df1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R2ff2eda74be94012"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R1209e8f35b2b455e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R2321d2533ffc4d89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R805204b35adf48fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R0ba95c649fe84e10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="Rac4482473ed24e77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R2edb51388f8b4289"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R9395eb4a9d054558"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Rdda5f68a7a9a48ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Re01005f1a7024e34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R3b3a46cb76c344ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="Red804cbbd55f4706"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R6b256234acbf4842"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R25cf82ae533e45d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R7b204abe6fa449f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R3ee6275dd8f74a4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="Rd5640b7e6b5f4816"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Raf72d9e6f1944518"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="Rc409cb3e34c44400"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="Rd3cc1c4a80c24a59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="R720282aa5c014064"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2933,6 +2934,41 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.5" customHeight="1">
+      <x:c r="A1" t="str">
+        <x:v>名前</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>エイブリン・オ・セルベリル</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19.5" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>出身地</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>？？？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19.5" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B3"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
